--- a/Contacts_zoho.xlsx
+++ b/Contacts_zoho.xlsx
@@ -84,7 +84,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:BP264"/>
+  <dimension ref="A1:BP268"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.53125" customWidth="true"/>
@@ -313,6 +313,11 @@
     <col min="224" max="224" width="19.53125" customWidth="true"/>
     <col min="225" max="225" width="19.53125" customWidth="true"/>
     <col min="226" max="226" width="19.53125" customWidth="true"/>
+    <col min="227" max="227" width="19.53125" customWidth="true"/>
+    <col min="228" max="228" width="19.53125" customWidth="true"/>
+    <col min="229" max="229" width="19.53125" customWidth="true"/>
+    <col min="230" max="230" width="19.53125" customWidth="true"/>
+    <col min="231" max="231" width="19.53125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22970,7 +22975,7 @@
         <v>45644.69070601852</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>45644.69070601852</v>
+        <v>46258.58667824074</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
@@ -22989,12 +22994,12 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>Jeleel</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Sodiq</t>
+          <t>Jeleel</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -23234,7 +23239,7 @@
       </c>
       <c r="BC68" s="2" t="inlineStr">
         <is>
-          <t>jaydaf2001@yahoo.co.uk</t>
+          <t>jeleel@optimumglobalcare.co.uk</t>
         </is>
       </c>
       <c r="BD68" s="2" t="inlineStr">
@@ -28716,7 +28721,7 @@
         <v>45700.61168981482</v>
       </c>
       <c r="B85" s="5" t="n">
-        <v>45700.61417824074</v>
+        <v>46274.4175</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
@@ -78064,7 +78069,7 @@
         <v>46069.57701388889</v>
       </c>
       <c r="B231" s="5" t="n">
-        <v>46069.57701388889</v>
+        <v>46263.62212962963</v>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
@@ -89546,6 +89551,1358 @@
         </is>
       </c>
       <c r="BP264" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="5" t="n">
+        <v>46261.44363425926</v>
+      </c>
+      <c r="B265" s="5" t="n">
+        <v>46280.74789351852</v>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>First Class Learning Reading Central</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>First Class Learning Reading Central</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>Mrs.</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>Sheetal</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>Keshari</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="J265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L265" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M265" s="2" t="inlineStr">
+        <is>
+          <t>accounts</t>
+        </is>
+      </c>
+      <c r="N265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P265" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q265" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="R265" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="S265" s="2" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="T265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U265" s="2" t="inlineStr">
+        <is>
+          <t>77 Chruch Lane</t>
+        </is>
+      </c>
+      <c r="V265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W265" s="2" t="inlineStr">
+        <is>
+          <t>Shinfield</t>
+        </is>
+      </c>
+      <c r="X265" s="2" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="Y265" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="Z265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA265" s="2" t="inlineStr">
+        <is>
+          <t>RG2 9BY</t>
+        </is>
+      </c>
+      <c r="AB265" s="2" t="inlineStr">
+        <is>
+          <t>+44-7787930767</t>
+        </is>
+      </c>
+      <c r="AC265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG265" s="2" t="inlineStr">
+        <is>
+          <t>77 Chruch Lane</t>
+        </is>
+      </c>
+      <c r="AH265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI265" s="2" t="inlineStr">
+        <is>
+          <t>Shinfield</t>
+        </is>
+      </c>
+      <c r="AJ265" s="2" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="AK265" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="AL265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM265" s="2" t="inlineStr">
+        <is>
+          <t>RG2 9BY</t>
+        </is>
+      </c>
+      <c r="AN265" s="2" t="inlineStr">
+        <is>
+          <t>+44-7787930767</t>
+        </is>
+      </c>
+      <c r="AO265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX265" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AY265" s="2" t="inlineStr">
+        <is>
+          <t>Your payment should reach us within 5 days from the invoice date</t>
+        </is>
+      </c>
+      <c r="AZ265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BB265" s="2" t="inlineStr">
+        <is>
+          <t>510492000001474002</t>
+        </is>
+      </c>
+      <c r="BC265" s="2" t="inlineStr">
+        <is>
+          <t>keshari.sheetal@gmail.com</t>
+        </is>
+      </c>
+      <c r="BD265" s="2" t="inlineStr">
+        <is>
+          <t>+44-7787930767</t>
+        </is>
+      </c>
+      <c r="BE265" s="2" t="inlineStr">
+        <is>
+          <t>510492000001474001</t>
+        </is>
+      </c>
+      <c r="BF265" s="2" t="inlineStr">
+        <is>
+          <t>First Class Learning Reading Central</t>
+        </is>
+      </c>
+      <c r="BG265" s="2" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="BH265" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="BI265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BJ265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM265" s="2" t="inlineStr">
+        <is>
+          <t>510492000001474001</t>
+        </is>
+      </c>
+      <c r="BN265" s="2" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="BO265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP265" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="5" t="n">
+        <v>46265.630011574074</v>
+      </c>
+      <c r="B266" s="5" t="n">
+        <v>46265.63269675926</v>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>SPOT CLEANERS LTD</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>SPOT CLEANERS LTD</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>Mr.</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>Timothy</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>Hopewell Zvikomborero Mutero</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="J266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L266" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M266" s="2" t="inlineStr">
+        <is>
+          <t>accounts</t>
+        </is>
+      </c>
+      <c r="N266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P266" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q266" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="R266" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="S266" s="2" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="T266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U266" s="2" t="inlineStr">
+        <is>
+          <t>2 Raymond Road</t>
+        </is>
+      </c>
+      <c r="V266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X266" s="2" t="inlineStr">
+        <is>
+          <t>Barnsley</t>
+        </is>
+      </c>
+      <c r="Y266" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="Z266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA266" s="2" t="inlineStr">
+        <is>
+          <t>S70 3JP</t>
+        </is>
+      </c>
+      <c r="AB266" s="2" t="inlineStr">
+        <is>
+          <t>+44-7466007884</t>
+        </is>
+      </c>
+      <c r="AC266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG266" s="2" t="inlineStr">
+        <is>
+          <t>2 Raymond Road</t>
+        </is>
+      </c>
+      <c r="AH266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ266" s="2" t="inlineStr">
+        <is>
+          <t>Barnsley</t>
+        </is>
+      </c>
+      <c r="AK266" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="AL266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM266" s="2" t="inlineStr">
+        <is>
+          <t>S70 3JP</t>
+        </is>
+      </c>
+      <c r="AN266" s="2" t="inlineStr">
+        <is>
+          <t>+44-7466007884</t>
+        </is>
+      </c>
+      <c r="AO266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX266" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AY266" s="2" t="inlineStr">
+        <is>
+          <t>Your payment should reach us within 5 days from the invoice date</t>
+        </is>
+      </c>
+      <c r="AZ266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BB266" s="2" t="inlineStr">
+        <is>
+          <t>510492000001488007</t>
+        </is>
+      </c>
+      <c r="BC266" s="2" t="inlineStr">
+        <is>
+          <t>admin@spotcleaners.co.uk</t>
+        </is>
+      </c>
+      <c r="BD266" s="2" t="inlineStr">
+        <is>
+          <t>+44-07466007884</t>
+        </is>
+      </c>
+      <c r="BE266" s="2" t="inlineStr">
+        <is>
+          <t>510492000001488006</t>
+        </is>
+      </c>
+      <c r="BF266" s="2" t="inlineStr">
+        <is>
+          <t>SPOT CLEANERS LTD</t>
+        </is>
+      </c>
+      <c r="BG266" s="2" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="BH266" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="BI266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BJ266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM266" s="2" t="inlineStr">
+        <is>
+          <t>510492000001488006</t>
+        </is>
+      </c>
+      <c r="BN266" s="2" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="BO266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP266" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="5" t="n">
+        <v>46272.55511574074</v>
+      </c>
+      <c r="B267" s="5" t="n">
+        <v>46274.391018518516</v>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>Mrs. Almina Dhalla</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>Kumon Wembley Park</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>Mrs.</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>Almina</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>Dhalla</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L267" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M267" s="2" t="inlineStr">
+        <is>
+          <t>accounts</t>
+        </is>
+      </c>
+      <c r="N267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P267" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q267" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="R267" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="S267" s="2" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="T267" s="2" t="inlineStr">
+        <is>
+          <t>Mr. Almina Dhalla</t>
+        </is>
+      </c>
+      <c r="U267" s="2" t="inlineStr">
+        <is>
+          <t>3 Woodridge way</t>
+        </is>
+      </c>
+      <c r="V267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W267" s="2" t="inlineStr">
+        <is>
+          <t>NorthWood</t>
+        </is>
+      </c>
+      <c r="X267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y267" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="Z267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA267" s="2" t="inlineStr">
+        <is>
+          <t>HA62BE</t>
+        </is>
+      </c>
+      <c r="AB267" s="2" t="inlineStr">
+        <is>
+          <t>+44-7922770140</t>
+        </is>
+      </c>
+      <c r="AC267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AK267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AN267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AO267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX267" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AY267" s="2" t="inlineStr">
+        <is>
+          <t>Your payment should reach us within 5 days from the invoice date</t>
+        </is>
+      </c>
+      <c r="AZ267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BB267" s="2" t="inlineStr">
+        <is>
+          <t>510492000001506004</t>
+        </is>
+      </c>
+      <c r="BC267" s="2" t="inlineStr">
+        <is>
+          <t>wembleypark@kumoncentre.co.uk</t>
+        </is>
+      </c>
+      <c r="BD267" s="2" t="inlineStr">
+        <is>
+          <t>+44-7922770140</t>
+        </is>
+      </c>
+      <c r="BE267" s="2" t="inlineStr">
+        <is>
+          <t>510492000001506003</t>
+        </is>
+      </c>
+      <c r="BF267" s="2" t="inlineStr">
+        <is>
+          <t>Mrs. Almina Dhalla</t>
+        </is>
+      </c>
+      <c r="BG267" s="2" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="BH267" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="BI267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BJ267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM267" s="2" t="inlineStr">
+        <is>
+          <t>510492000001506003</t>
+        </is>
+      </c>
+      <c r="BN267" s="2" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="BO267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP267" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="5" t="n">
+        <v>46277.54399305556</v>
+      </c>
+      <c r="B268" s="5" t="n">
+        <v>46277.54399305556</v>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>Max Out Tutoring</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>Max Out Tutoring</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>Mr.</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>Moyo</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>Sankofa</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="J268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L268" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M268" s="2" t="inlineStr">
+        <is>
+          <t>accounts</t>
+        </is>
+      </c>
+      <c r="N268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P268" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q268" s="2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="R268" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="S268" s="2" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="T268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U268" s="2" t="inlineStr">
+        <is>
+          <t>17 Claverdill Road</t>
+        </is>
+      </c>
+      <c r="V268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X268" s="2" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="Y268" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="Z268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA268" s="2" t="inlineStr">
+        <is>
+          <t>SW2 2DJ</t>
+        </is>
+      </c>
+      <c r="AB268" s="2" t="inlineStr">
+        <is>
+          <t>+44-7948800975</t>
+        </is>
+      </c>
+      <c r="AC268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG268" s="2" t="inlineStr">
+        <is>
+          <t>17 Claverdill Road</t>
+        </is>
+      </c>
+      <c r="AH268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ268" s="2" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="AK268" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="AL268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM268" s="2" t="inlineStr">
+        <is>
+          <t>SW2 2DJ</t>
+        </is>
+      </c>
+      <c r="AN268" s="2" t="inlineStr">
+        <is>
+          <t>+44-7948800975</t>
+        </is>
+      </c>
+      <c r="AO268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AP268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AQ268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AR268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AS268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AT268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX268" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AY268" s="2" t="inlineStr">
+        <is>
+          <t>Your payment should reach us within 5 days from the invoice date</t>
+        </is>
+      </c>
+      <c r="AZ268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BB268" s="2" t="inlineStr">
+        <is>
+          <t>510492000001517002</t>
+        </is>
+      </c>
+      <c r="BC268" s="2" t="inlineStr">
+        <is>
+          <t>moyotheteacher@outlook.com</t>
+        </is>
+      </c>
+      <c r="BD268" s="2" t="inlineStr">
+        <is>
+          <t>+44-7948800975</t>
+        </is>
+      </c>
+      <c r="BE268" s="2" t="inlineStr">
+        <is>
+          <t>510492000001517001</t>
+        </is>
+      </c>
+      <c r="BF268" s="2" t="inlineStr">
+        <is>
+          <t>Max Out Tutoring</t>
+        </is>
+      </c>
+      <c r="BG268" s="2" t="inlineStr">
+        <is>
+          <t>customer</t>
+        </is>
+      </c>
+      <c r="BH268" s="2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="BI268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BJ268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BK268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BL268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BM268" s="2" t="inlineStr">
+        <is>
+          <t>510492000001517001</t>
+        </is>
+      </c>
+      <c r="BN268" s="2" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="BO268" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BP268" s="2" t="inlineStr">
         <is>
           <t/>
         </is>
